--- a/glosarium.xlsx
+++ b/glosarium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ziada\Documents\draft-latex\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2C1ED1F-2FE7-47CA-95B3-027B142C8BCF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FAD2FAB-3681-42A5-AA01-835EF211CE5F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{E3DF4BDF-6501-45BB-AF14-E305AA3C41A9}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
   <si>
     <t>No</t>
   </si>
@@ -127,6 +127,345 @@
   </si>
   <si>
     <t>Jeda waktu yang terjadi antara saat sebuah perintah atau data dikirim dari suatu titik ke titik lainnya (misalnya dari sensor ke server) hingga saat diterima atau direspon</t>
+  </si>
+  <si>
+    <t>resource-constrained</t>
+  </si>
+  <si>
+    <t>PIP</t>
+  </si>
+  <si>
+    <t>Policy Information Point</t>
+  </si>
+  <si>
+    <t>Cloud</t>
+  </si>
+  <si>
+    <t>Bottleneck</t>
+  </si>
+  <si>
+    <t>PIP Calls</t>
+  </si>
+  <si>
+    <t>overhead</t>
+  </si>
+  <si>
+    <t>node</t>
+  </si>
+  <si>
+    <t>freshness attribute</t>
+  </si>
+  <si>
+    <t>PDP</t>
+  </si>
+  <si>
+    <t>Policy Decision Point</t>
+  </si>
+  <si>
+    <t>attribute handling</t>
+  </si>
+  <si>
+    <t>IAM</t>
+  </si>
+  <si>
+    <t>Identity and Access Management</t>
+  </si>
+  <si>
+    <t>trade-off</t>
+  </si>
+  <si>
+    <t>local caching</t>
+  </si>
+  <si>
+    <t>stale attribute</t>
+  </si>
+  <si>
+    <t>trustworthiness</t>
+  </si>
+  <si>
+    <t>false allow</t>
+  </si>
+  <si>
+    <t>false deny</t>
+  </si>
+  <si>
+    <t>revocation notification</t>
+  </si>
+  <si>
+    <t>freshness treshold</t>
+  </si>
+  <si>
+    <t>cache hit</t>
+  </si>
+  <si>
+    <t>retrieval cost</t>
+  </si>
+  <si>
+    <t>SLA</t>
+  </si>
+  <si>
+    <t>Service Level Agreement</t>
+  </si>
+  <si>
+    <t>TTL</t>
+  </si>
+  <si>
+    <t>Time-to-Live</t>
+  </si>
+  <si>
+    <t>edge</t>
+  </si>
+  <si>
+    <t>fog</t>
+  </si>
+  <si>
+    <t>cache management</t>
+  </si>
+  <si>
+    <t>LAA</t>
+  </si>
+  <si>
+    <t>Local Authentication and Authorization</t>
+  </si>
+  <si>
+    <t>zero-trust</t>
+  </si>
+  <si>
+    <t>GWO</t>
+  </si>
+  <si>
+    <t>Grey Wolf Optimization</t>
+  </si>
+  <si>
+    <t>task schedulling</t>
+  </si>
+  <si>
+    <t>makespan</t>
+  </si>
+  <si>
+    <t>ACO</t>
+  </si>
+  <si>
+    <t>Ant Colony Optimization</t>
+  </si>
+  <si>
+    <t>random search</t>
+  </si>
+  <si>
+    <t>false allow rate</t>
+  </si>
+  <si>
+    <t>false deny rate</t>
+  </si>
+  <si>
+    <t>stale cache hit rate</t>
+  </si>
+  <si>
+    <t>revocation false allow rate</t>
+  </si>
+  <si>
+    <t>firmware</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>critical request</t>
+  </si>
+  <si>
+    <t>PIP unavailability</t>
+  </si>
+  <si>
+    <t>revocation event</t>
+  </si>
+  <si>
+    <t>RBAC</t>
+  </si>
+  <si>
+    <t>Role-Based Access Control</t>
+  </si>
+  <si>
+    <t>DAC</t>
+  </si>
+  <si>
+    <t>Discretionary Access Control</t>
+  </si>
+  <si>
+    <t>MAC</t>
+  </si>
+  <si>
+    <t>Mandatory Access Control</t>
+  </si>
+  <si>
+    <t>UCON</t>
+  </si>
+  <si>
+    <t>Usage Control</t>
+  </si>
+  <si>
+    <t>CapBAC</t>
+  </si>
+  <si>
+    <t>Capability-Based Access Control</t>
+  </si>
+  <si>
+    <t>workload</t>
+  </si>
+  <si>
+    <t>endpoint</t>
+  </si>
+  <si>
+    <t>Keterbatasan sumber daya pada perangkat (seperti daya pemrosesan, memori, atau baterai) yang memerlukan desain efisien dalam komputasi dan komunikasi.</t>
+  </si>
+  <si>
+    <t>Komponen dalam arsitektur kontrol akses (ABAC) yang menyediakan atribut yang diperlukan untuk mengambil keputusan izin, misalnya atribut pengguna, lingkungan, atau sumber daya.</t>
+  </si>
+  <si>
+    <t>Pusat komputasi jarak jauh dengan sumber daya besar (server, storage) yang dapat diakses melalui internet, biasanya memiliki latensi lebih tinggi dibandingkan edge/fog.</t>
+  </si>
+  <si>
+    <t>Titik dalam sistem yang membatasi kinerja keseluruhan karena kapasitasnya lebih rendah daripada beban yang diterima, misalnya jaringan, server, atau komponen pemrosesan.</t>
+  </si>
+  <si>
+    <t>Permintaan yang dikirim oleh PDP ke PIP untuk mengambil nilai atribut tertentu saat evaluasi kebijakan.</t>
+  </si>
+  <si>
+    <t>Sumber daya tambahan (waktu, memori, bandwidth) yang dikonsumsi oleh suatu mekanisme (misalnya keamanan, logging) di luar pemrosesan utama.</t>
+  </si>
+  <si>
+    <t>Entitas dalam jaringan (misalnya perangkat IoT, sensor, gateway, server) yang dapat memproses, mengirim, atau menerima data.</t>
+  </si>
+  <si>
+    <t>Atribut yang menunjukkan seberapa baru atau mutakhir suatu data/cache, biasanya berupa stempel waktu atau versi.</t>
+  </si>
+  <si>
+    <t>Komponen yang mengevaluasi kebijakan dan memutuskan apakah suatu permintaan akses diizinkan atau ditolak berdasarkan atribut yang diberikan.</t>
+  </si>
+  <si>
+    <t>Proses pengelolaan atribut (pengambilan, validasi, pembaruan, caching) yang digunakan untuk keputusan kontrol akses.</t>
+  </si>
+  <si>
+    <t>Kerangka kerja kebijakan dan teknologi untuk mengelola identitas digital dan mengatur akses pengguna ke sumber daya.</t>
+  </si>
+  <si>
+    <t>Situasi di mana peningkatan satu aspek (misalnya kecepatan) mengorbankan aspek lain (misalnya keakuratan atau keamanan), yang memerlukan keseimbangan desain.</t>
+  </si>
+  <si>
+    <t>Penyimpanan sementara data (misalnya atribut) di perangkat lokal untuk mengurangi kebutuhan pengambilan ulang dari sumber jarak jauh.</t>
+  </si>
+  <si>
+    <t>Atribut yang sudah tidak mutakhir karena belum diperbarui sesuai perubahan kondisi sebenarnya.</t>
+  </si>
+  <si>
+    <t>Tingkat keyakinan bahwa suatu entitas (perangkat, data, pengguna) dapat diandalkan, aman, dan berperilaku sesuai harapan.</t>
+  </si>
+  <si>
+    <t>Kondisi di mana sistem kontrol akses secara keliru mengizinkan akses yang seharusnya ditolak (false positive dalam keamanan).</t>
+  </si>
+  <si>
+    <t>Kondisi di mana sistem kontrol akses secara keliru menolak akses yang seharusnya diizinkan (false negative dalam keamanan).</t>
+  </si>
+  <si>
+    <t>Pesan yang dikirim untuk memberi tahu bahwa hak akses sebelumnya telah dicabut, sehingga cache atribut harus dibatalkan.</t>
+  </si>
+  <si>
+    <t>Batas maksimal usia data (misalnya dalam detik) yang masih dianggap mutakhir; atribut yang lebih tua dianggap basi (stale).</t>
+  </si>
+  <si>
+    <t>Situasi ketika data yang diminta ditemukan dalam cache lokal, sehingga tidak perlu mengambil dari sumber asli.</t>
+  </si>
+  <si>
+    <t>Biaya (latensi, bandwidth, energi) yang diperlukan untuk mengambil data dari sumber jarak jauh dibandingkan dari cache.</t>
+  </si>
+  <si>
+    <t>Kesepakatan antara penyedia layanan dan pengguna mengenai tingkat kinerja yang dijamin, misalnya latensi maksimum atau ketersediaan.</t>
+  </si>
+  <si>
+    <t>Nilai waktu atau hop yang menentukan berapa lama suatu data (cache) dianggap valid sebelum harus diperbarui atau dihapus.</t>
+  </si>
+  <si>
+    <t>Lapisan komputasi yang dekat dengan sumber data (misalnya gateway atau router) untuk mengurangi latensi dan beban jaringan.</t>
+  </si>
+  <si>
+    <t>Lapisan komputasi antara edge dan cloud yang menyediakan penyimpanan dan pemrosesan lebih terdistribusi, dengan jangkauan lebih luas dari edge.</t>
+  </si>
+  <si>
+    <t>Mekanisme untuk mengontrol isi cache (penyimpanan, pembaruan, penghapusan, validasi) demi efisiensi dan keakuratan.</t>
+  </si>
+  <si>
+    <t>cache</t>
+  </si>
+  <si>
+    <t>Model otorisasi berbasis atribut yang dioptimalkan untuk perangkat dengan sumber daya terbatas (resource-constrained).</t>
+  </si>
+  <si>
+    <t>Model keamanan yang tidak secara otomatis mempercayai siapa pun di dalam atau luar jaringan; setiap akses harus diverifikasi secara berkelanjutan.</t>
+  </si>
+  <si>
+    <t>Algoritma optimasi metaheuristik terinspirasi dari perilaku hierarki dan berburu serigala abu-abu, digunakan untuk penjadwalan tugas.</t>
+  </si>
+  <si>
+    <t>Proses penjadwalan dan alokasi tugas komputasi ke berbagai node (edge, fog, cloud) untuk memenuhi tujuan seperti meminimalkan waktu penyelesaian.</t>
+  </si>
+  <si>
+    <t>Total waktu yang diperlukan untuk menyelesaikan sekumpulan tugas dari awal hingga akhir dalam penjadwalan.</t>
+  </si>
+  <si>
+    <t>Algoritma optimasi terinspirasi dari perilaku semut mencari jalur terpendek, digunakan untuk masalah routing dan penjadwalan.</t>
+  </si>
+  <si>
+    <t>Metode optimasi sederhana yang mencoba solusi secara acak dalam ruang pencarian; digunakan sebagai baseline atau untuk eksplorasi awal.</t>
+  </si>
+  <si>
+    <t>Frekuensi (atau probabilitas) terjadinya false allow relatif terhadap total permintaan akses yang seharusnya ditolak.</t>
+  </si>
+  <si>
+    <t>Frekuensi terjadinya false deny relatif terhadap total permintaan akses yang seharusnya diizinkan.</t>
+  </si>
+  <si>
+    <t>Tingkat cache hit yang terjadi pada atribut yang sudah basi (stale), yang dapat menyebabkan keputusan akses salah.</t>
+  </si>
+  <si>
+    <t>Frekuensi false allow yang terjadi karena cache atribut tidak segera diperbarui setelah adanya event pencabutan (revocation).</t>
+  </si>
+  <si>
+    <t>Perangkat lunak tingkat rendah yang tertanam dalam perangkat keras (misalnya sensor IoT) untuk mengontrol fungsionalitas dasarnya.</t>
+  </si>
+  <si>
+    <t>Kumpulan izin atau hak akses yang dikelompokkan berdasarkan fungsi pengguna dalam organisasi (digunakan dalam RBAC).</t>
+  </si>
+  <si>
+    <t>Permintaan akses atau tugas yang memiliki prioritas tinggi atau dampak keamanan/keselamatan besar jika terjadi kesalahan.</t>
+  </si>
+  <si>
+    <t>Kondisi ketika komponen PIP tidak dapat diakses (misalnya karena jaringan putus atau server down), sehingga atribut tidak dapat diambil secara langsung.</t>
+  </si>
+  <si>
+    <t>Kejadian di mana hak akses yang sebelumnya diberikan dicabut, misalnya karena pengguna keluar atau atribut berubah.</t>
+  </si>
+  <si>
+    <t>Model kontrol akses di mana izin diberikan berdasarkan peran pengguna dalam organisasi.</t>
+  </si>
+  <si>
+    <t>Model kontrol akses di mana pemilik sumber daya dapat secara bebas menentukan siapa saja yang dapat mengakses sumber daya tersebut.</t>
+  </si>
+  <si>
+    <t>Model kontrol akses di mana kebijakan ditentukan oleh otoritas pusat berdasarkan klasifikasi data dan izin pengguna, tidak dapat diubah oleh pemilik.</t>
+  </si>
+  <si>
+    <t>Model kontrol akses yang memperluas konsep tradisional dengan mempertimbangkan atribut mutabilitas, kewajiban, dan kondisi penggunaan berkelanjutan.</t>
+  </si>
+  <si>
+    <t>Model kontrol akses di mana izin diberikan melalui token (capability) yang tidak dapat dipalsukan dan dapat didelegasikan.</t>
+  </si>
+  <si>
+    <t>Beban pemrosesan atau permintaan yang harus ditangani oleh suatu node (edge, fog, cloud) dalam periode waktu tertentu.</t>
+  </si>
+  <si>
+    <t>Perangkat ujung dalam jaringan, seperti sensor IoT, aktuator, ponsel, atau komputer pengguna, yang menjadi sumber atau tujuan data.</t>
+  </si>
+  <si>
+    <t>Lapisan penyimpanan sementara berkecepatan tinggi yang menyimpan salinan data yang sering diakses atau baru saja digunakan, bertujuan untuk mengurangi waktu pengambilan data dari sumber asli (misalnya server atau database).</t>
   </si>
 </sst>
 </file>
@@ -487,7 +826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD84CBED-B90C-4DC8-9DCF-CBDBFF805F3A}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.36328125" bestFit="1" customWidth="1"/>
@@ -616,6 +955,445 @@
         <v>31</v>
       </c>
     </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B33" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B35" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" t="s">
+        <v>59</v>
+      </c>
+      <c r="D35" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B36" t="s">
+        <v>60</v>
+      </c>
+      <c r="D36" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D37" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B38" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B39" t="s">
+        <v>63</v>
+      </c>
+      <c r="C39" t="s">
+        <v>64</v>
+      </c>
+      <c r="D39" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B40" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B41" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D41" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B42" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B43" t="s">
+        <v>69</v>
+      </c>
+      <c r="D43" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B44" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" t="s">
+        <v>71</v>
+      </c>
+      <c r="D44" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B45" t="s">
+        <v>72</v>
+      </c>
+      <c r="D45" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B46" t="s">
+        <v>73</v>
+      </c>
+      <c r="D46" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B47" t="s">
+        <v>74</v>
+      </c>
+      <c r="D47" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B48" t="s">
+        <v>75</v>
+      </c>
+      <c r="D48" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B49" t="s">
+        <v>76</v>
+      </c>
+      <c r="D49" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B50" t="s">
+        <v>77</v>
+      </c>
+      <c r="D50" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B51" t="s">
+        <v>78</v>
+      </c>
+      <c r="D51" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B52" t="s">
+        <v>79</v>
+      </c>
+      <c r="D52" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B53" t="s">
+        <v>80</v>
+      </c>
+      <c r="D53" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B54" t="s">
+        <v>81</v>
+      </c>
+      <c r="D54" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B55" t="s">
+        <v>82</v>
+      </c>
+      <c r="C55" t="s">
+        <v>83</v>
+      </c>
+      <c r="D55" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B56" t="s">
+        <v>84</v>
+      </c>
+      <c r="C56" t="s">
+        <v>85</v>
+      </c>
+      <c r="D56" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B57" t="s">
+        <v>86</v>
+      </c>
+      <c r="C57" t="s">
+        <v>87</v>
+      </c>
+      <c r="D57" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B58" t="s">
+        <v>88</v>
+      </c>
+      <c r="C58" t="s">
+        <v>89</v>
+      </c>
+      <c r="D58" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B59" t="s">
+        <v>90</v>
+      </c>
+      <c r="C59" t="s">
+        <v>91</v>
+      </c>
+      <c r="D59" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B60" t="s">
+        <v>92</v>
+      </c>
+      <c r="D60" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B61" t="s">
+        <v>93</v>
+      </c>
+      <c r="D61" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B62" t="s">
+        <v>120</v>
+      </c>
+      <c r="D62" t="s">
+        <v>144</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
